--- a/output/full_scan/batch_seq0_2026-09-21.xlsx
+++ b/output/full_scan/batch_seq0_2026-09-21.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>8150</v>
+        <v>8227</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>892.8811559791201</v>
+        <v>922.1445850821844</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>103</v>
+        <v>287.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.30029749733748</v>
+        <v>80.70660318178669</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>13.08013464907763</v>
+        <v>42.88248264399843</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.683168315422159</v>
+        <v>0.3144585082184313</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1.074839688294487</v>
+        <v>10.53761634343245</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8111</v>
+        <v>8150</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>825.8092074254574</v>
+        <v>892.8811559791201</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>80.59999999999999</v>
+        <v>103</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,13 +605,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>67.12764382490059</v>
+        <v>66.30029749733748</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>31.97503178780717</v>
+        <v>13.08013464907763</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.180920742545748</v>
+        <v>2.683168315422159</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4683608662760892</v>
+        <v>1.074839688294487</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8215</v>
+        <v>8111</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>812.5080353501452</v>
+        <v>825.8092074254574</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>30.05</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>73.92773447227033</v>
+        <v>67.12764382490059</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>25.11971314785726</v>
+        <v>31.97503178780717</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.850803535014513</v>
+        <v>2.180920742545748</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.425614067052381</v>
+        <v>0.4683608662760892</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8040</v>
+        <v>8215</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>799.4581294690242</v>
+        <v>812.5080353501452</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>83.5</v>
+        <v>30.05</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>60.38096760546191</v>
+        <v>73.92773447227033</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>16.20008239983458</v>
+        <v>25.11971314785726</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.938163415218918</v>
+        <v>4.850803535014513</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.7351343296548885</v>
+        <v>0.425614067052381</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8299</v>
+        <v>8040</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>774.8858963724512</v>
+        <v>799.4581294690242</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2150</v>
+        <v>83.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>57.67868742687828</v>
+        <v>60.38096760546191</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10.8573571825937</v>
+        <v>16.20008239983458</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.077869270996324</v>
+        <v>1.938163415218918</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>4.608776209456108</v>
+        <v>0.7351343296548885</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8097</v>
+        <v>8299</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>746.3353390608014</v>
+        <v>774.8858963724512</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>49.65</v>
+        <v>2150</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>52.06807712706949</v>
+        <v>57.67868742687828</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>34.64161028799499</v>
+        <v>10.8573571825937</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.486809415765888</v>
+        <v>1.077869270996324</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.243128891959994</v>
+        <v>4.608776209456108</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8110</v>
+        <v>8097</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>744</v>
+        <v>746.3353390608014</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>52.1</v>
+        <v>49.65</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>71.37529868936574</v>
+        <v>52.06807712706949</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>14.83267941075974</v>
+        <v>34.64161028799499</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>6.139560807080262</v>
+        <v>2.486809415765888</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.7406695635397952</v>
+        <v>0.243128891959994</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8059</v>
+        <v>8110</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>702.2906479091724</v>
+        <v>744</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>20.15</v>
+        <v>52.1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>80.58498622503441</v>
+        <v>71.37529868936574</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>21.36277832979288</v>
+        <v>14.83267941075974</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.649545685672977</v>
+        <v>6.139560807080262</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4831668449826743</v>
+        <v>0.7406695635397952</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, williams_r_recovery, cci_momentum, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8089</v>
+        <v>8059</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>698.1704315185511</v>
+        <v>702.2906479091724</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>19.95</v>
+        <v>20.15</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>71.03783010322375</v>
+        <v>80.58498622503441</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15.50647219428221</v>
+        <v>21.36277832979288</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.417043151855109</v>
+        <v>1.649545685672977</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2453576612557537</v>
+        <v>0.4831668449826743</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, williams_r_recovery, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8932</v>
+        <v>8089</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>664.1087324022783</v>
+        <v>698.1704315185511</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>94.90000000000001</v>
+        <v>19.95</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>48.56624909301794</v>
+        <v>71.03783010322375</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>22.24690655223865</v>
+        <v>15.50647219428221</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.672653509829275</v>
+        <v>3.417043151855109</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.37270829882871</v>
+        <v>0.2453576612557537</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8171</v>
+        <v>8932</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>650.8723671845833</v>
+        <v>664.1087324022783</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>20.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>56.98090749217756</v>
+        <v>48.56624909301794</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>14.04688139891691</v>
+        <v>22.24690655223865</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.8735036475381072</v>
+        <v>0.672653509829275</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0645593836754333</v>
+        <v>0.37270829882871</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8431</v>
+        <v>8171</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>621.9372040374948</v>
+        <v>650.8723671845833</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>20.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.59378649126881</v>
+        <v>56.98090749217756</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>30.60683012194108</v>
+        <v>14.04688139891691</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.464609264892221</v>
+        <v>0.8735036475381072</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.1327507128543255</v>
+        <v>0.0645593836754333</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8064</v>
+        <v>8431</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>594.0275531534221</v>
+        <v>621.9372040374948</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>138</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>65.47656298102815</v>
+        <v>60.59378649126881</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>16.49883980413157</v>
+        <v>30.60683012194108</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.806185088957205</v>
+        <v>1.464609264892221</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>2.410067672663559</v>
+        <v>0.1327507128543255</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8466</v>
+        <v>8064</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>590.7539870012615</v>
+        <v>594.0275531534221</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>15.75</v>
+        <v>138</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>58.16805052044296</v>
+        <v>65.47656298102815</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>42.69583121638751</v>
+        <v>16.49883980413157</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>5.894165849154597</v>
+        <v>1.806185088957205</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.07864741177015409</v>
+        <v>2.410067672663559</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8050</v>
+        <v>8466</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>572.6793098308807</v>
+        <v>590.7539870012615</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>59.1</v>
+        <v>15.75</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>56.70442996142083</v>
+        <v>58.16805052044296</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>11.22603245562289</v>
+        <v>42.69583121638751</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.8316310983209935</v>
+        <v>5.894165849154597</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.4782851846123896</v>
+        <v>0.07864741177015409</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8072</v>
+        <v>8050</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>554.4470345852028</v>
+        <v>572.6793098308807</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>27.5</v>
+        <v>59.1</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>62.08881907858512</v>
+        <v>56.70442996142083</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>28.64415198018714</v>
+        <v>11.22603245562289</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.072714567803813</v>
+        <v>0.8316310983209935</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.2007559485065073</v>
+        <v>0.4782851846123896</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8277</v>
+        <v>8072</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>539.0555225093543</v>
+        <v>554.4470345852028</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>16.85</v>
+        <v>27.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>94.97971651263728</v>
+        <v>62.08881907858512</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>20.19728419776968</v>
+        <v>28.64415198018714</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.001253357962998</v>
+        <v>1.072714567803813</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.5818898678802065</v>
+        <v>0.2007559485065073</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8054</v>
+        <v>8277</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>529.5013021071259</v>
+        <v>539.0555225093543</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>84.90000000000001</v>
+        <v>16.85</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>53.76628247266168</v>
+        <v>94.97971651263728</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>10.1776031725165</v>
+        <v>20.19728419776968</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.023550902434007</v>
+        <v>2.001253357962998</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.5878463255504152</v>
+        <v>0.5818898678802065</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8240</v>
+        <v>8054</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>519.6987566804704</v>
+        <v>529.5013021071259</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>51.1</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>58.10113584890307</v>
+        <v>53.76628247266168</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>29.0748351148268</v>
+        <v>10.1776031725165</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.2803146417342701</v>
+        <v>1.023550902434007</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.1044537254313264</v>
+        <v>0.5878463255504152</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8472</v>
+        <v>8240</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>519.5515338575324</v>
+        <v>519.6987566804704</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>77.8</v>
+        <v>51.1</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>58.86885305919947</v>
+        <v>58.10113584890307</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>30.78047249482836</v>
+        <v>29.0748351148268</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.2413283901724565</v>
+        <v>0.2803146417342701</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.4554240528333939</v>
+        <v>-0.1044537254313264</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8131</v>
+        <v>8472</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>507.7372293486442</v>
+        <v>519.5515338575324</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>61.7</v>
+        <v>77.8</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>49.65863806699912</v>
+        <v>58.86885305919947</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>10.04834965401513</v>
+        <v>30.78047249482836</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.341386861194855</v>
+        <v>0.2413283901724565</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.0983498960042108</v>
+        <v>0.4554240528333939</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8183</v>
+        <v>8131</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>492</v>
+        <v>507.7372293486442</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>28.9</v>
+        <v>61.7</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>51.06402788629106</v>
+        <v>49.65863806699912</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>19.84395671476716</v>
+        <v>10.04834965401513</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7.104897331332199</v>
+        <v>1.341386861194855</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0707157601726367</v>
+        <v>0.0983498960042108</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8080</v>
+        <v>8183</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>491.8419005290465</v>
+        <v>492</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>28.85</v>
+        <v>28.9</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>53.67765902153598</v>
+        <v>51.06402788629106</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>48.19650856860687</v>
+        <v>19.84395671476716</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.806991980600285</v>
+        <v>7.104897331332199</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.0354177456138158</v>
+        <v>0.0707157601726367</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8182</v>
+        <v>8080</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>478.8286341210836</v>
+        <v>491.8419005290465</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>39.55</v>
+        <v>28.85</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>50.31439054933337</v>
+        <v>53.67765902153598</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>9.710931761427664</v>
+        <v>48.19650856860687</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.209563980526576</v>
+        <v>0.806991980600285</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.1654319939685778</v>
+        <v>-0.0354177456138158</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8488</v>
+        <v>8182</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>461.6822935279448</v>
+        <v>478.8286341210836</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>9.91</v>
+        <v>39.55</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>47.54035852853748</v>
+        <v>50.31439054933337</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>32.49108953701606</v>
+        <v>9.710931761427664</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.2948340999019931</v>
+        <v>1.209563980526576</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0225393857491252</v>
+        <v>0.1654319939685778</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8289</v>
+        <v>8488</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>453.8698924842612</v>
+        <v>461.6822935279448</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>44.25</v>
+        <v>9.91</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>48.8591933130301</v>
+        <v>47.54035852853748</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>21.95730265377238</v>
+        <v>32.49108953701606</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.672289760534683</v>
+        <v>0.2948340999019931</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1375910513753506</v>
+        <v>-0.0225393857491252</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8109</v>
+        <v>8289</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>446.899446613678</v>
+        <v>453.8698924842612</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>133.5</v>
+        <v>44.25</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.87281945524191</v>
+        <v>48.8591933130301</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>20.93025582846468</v>
+        <v>21.95730265377238</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4670167902641234</v>
+        <v>1.672289760534683</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.4056205687288533</v>
+        <v>0.1375910513753506</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8213</v>
+        <v>8109</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>445.5293402419802</v>
+        <v>446.899446613678</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>33.2</v>
+        <v>133.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>55.48344007423933</v>
+        <v>56.87281945524191</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>11.94959581653037</v>
+        <v>20.93025582846468</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.023489348064328</v>
+        <v>0.4670167902641234</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0157044818588665</v>
+        <v>0.4056205687288533</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8048</v>
+        <v>8213</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>431.3994297184127</v>
+        <v>445.5293402419802</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>49.5</v>
+        <v>33.2</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>43.22458979166434</v>
+        <v>55.48344007423933</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>16.98589412107349</v>
+        <v>11.94959581653037</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.095927180373886</v>
+        <v>1.023489348064328</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0574288240533467</v>
+        <v>0.0157044818588665</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8103</v>
+        <v>8048</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>430.0120457294294</v>
+        <v>431.3994297184127</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>128.5</v>
+        <v>49.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>67.12465986096336</v>
+        <v>43.22458979166434</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>40.71608265414174</v>
+        <v>16.98589412107349</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.195834484688414</v>
+        <v>1.095927180373886</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.3422505034817806</v>
+        <v>0.0574288240533467</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8070</v>
+        <v>8103</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>426.3781922240279</v>
+        <v>430.0120457294294</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>49.9</v>
+        <v>128.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>50.3285057762516</v>
+        <v>67.12465986096336</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>15.75944752990423</v>
+        <v>40.71608265414174</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6691887791698611</v>
+        <v>1.195834484688414</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.0023238773709039</v>
+        <v>0.3422505034817806</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8383</v>
+        <v>8070</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>425.8426158633799</v>
+        <v>426.3781922240279</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>67</v>
+        <v>49.9</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>50.24829353020551</v>
+        <v>50.3285057762516</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>9.610213007099969</v>
+        <v>15.75944752990423</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6157697839671751</v>
+        <v>0.6691887791698611</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.4438412859236784</v>
+        <v>-0.0023238773709039</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2223,21 +2223,21 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8442</v>
+        <v>8383</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>425.6892527895638</v>
+        <v>425.8426158633799</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>46.2</v>
+        <v>67</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>55.03413375588747</v>
+        <v>50.24829353020551</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>10.66906682861003</v>
+        <v>9.610213007099969</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5779819685876546</v>
+        <v>0.6157697839671751</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.0396102887538626</v>
+        <v>0.4438412859236784</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8091</v>
+        <v>8442</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>425.59206364454</v>
+        <v>425.6892527895638</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>215.5</v>
+        <v>46.2</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>47.73595327281181</v>
+        <v>55.03413375588747</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>14.98659997967605</v>
+        <v>10.66906682861003</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.7134761532741926</v>
+        <v>0.5779819685876546</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>1.200707415521419</v>
+        <v>-0.0396102887538626</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8047</v>
+        <v>8091</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>424.2957224791141</v>
+        <v>425.59206364454</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>45.8</v>
+        <v>215.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>51.86676735222642</v>
+        <v>47.73595327281181</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>11.03762534102128</v>
+        <v>14.98659997967605</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.6900817675537453</v>
+        <v>0.7134761532741926</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.2887537715300727</v>
+        <v>1.200707415521419</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8086</v>
+        <v>8047</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>421.060135464391</v>
+        <v>424.2957224791141</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>109.5</v>
+        <v>45.8</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>44.73442794230218</v>
+        <v>51.86676735222642</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>18.59654304380264</v>
+        <v>11.03762534102128</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4651838673087293</v>
+        <v>0.6900817675537453</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.1431094509375263</v>
+        <v>0.2887537715300727</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8147</v>
+        <v>8086</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>414.5927915673938</v>
+        <v>421.060135464391</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>135.5</v>
+        <v>109.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>57.52559888268281</v>
+        <v>44.73442794230218</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18.3301543289514</v>
+        <v>18.59654304380264</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.5454571034302519</v>
+        <v>0.4651838673087293</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.35991692161132</v>
+        <v>0.1431094509375263</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8045</v>
+        <v>8147</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>413.2372559721557</v>
+        <v>414.5927915673938</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>53.8</v>
+        <v>135.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>55.73896120725847</v>
+        <v>57.52559888268281</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20.43916784974801</v>
+        <v>18.3301543289514</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9548312112756974</v>
+        <v>0.5454571034302519</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.8004318212431016</v>
+        <v>0.35991692161132</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8043</v>
+        <v>8045</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>412.1708806967652</v>
+        <v>413.2372559721557</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>132.5</v>
+        <v>53.8</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>44.80134746083409</v>
+        <v>55.73896120725847</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>11.08463869306909</v>
+        <v>20.43916784974801</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3974741194455025</v>
+        <v>0.9548312112756974</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.5449130710550123</v>
+        <v>0.8004318212431016</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8042</v>
+        <v>8043</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>405.3986793561333</v>
+        <v>412.1708806967652</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>113.5</v>
+        <v>132.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>50.88628727020855</v>
+        <v>44.80134746083409</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>14.98056564147085</v>
+        <v>11.08463869306909</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.6660737357727123</v>
+        <v>0.3974741194455025</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.912978463939686</v>
+        <v>-0.5449130710550123</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8201</v>
+        <v>8042</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>394.9632895409773</v>
+        <v>405.3986793561333</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>12</v>
+        <v>113.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>53.84806756060817</v>
+        <v>50.88628727020855</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>32.45141759869131</v>
+        <v>14.98056564147085</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.09186450412997101</v>
+        <v>0.6660737357727123</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0374180755666534</v>
+        <v>0.912978463939686</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8162</v>
+        <v>8201</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>391.1504317152512</v>
+        <v>394.9632895409773</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>60.4</v>
+        <v>12</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>49.43083573099091</v>
+        <v>53.84806756060817</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>10.99099099695525</v>
+        <v>32.45141759869131</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.518981686828493</v>
+        <v>0.09186450412997101</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.07008019555247701</v>
+        <v>0.0374180755666534</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8104</v>
+        <v>8162</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>389.1539854957771</v>
+        <v>391.1504317152512</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>31.2</v>
+        <v>60.4</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>53.50332930661291</v>
+        <v>49.43083573099091</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>21.76525262602678</v>
+        <v>10.99099099695525</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.619977698359118</v>
+        <v>1.518981686828493</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1925517535438951</v>
+        <v>-0.07008019555247701</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8261</v>
+        <v>8104</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>386.9975112302079</v>
+        <v>389.1539854957771</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>173.5</v>
+        <v>31.2</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>46.37578121156662</v>
+        <v>53.50332930661291</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>11.60702726947961</v>
+        <v>21.76525262602678</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4989765271771578</v>
+        <v>1.619977698359118</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.5307086015519</v>
+        <v>0.1925517535438951</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8411</v>
+        <v>8261</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>382.3215806818214</v>
+        <v>386.9975112302079</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>12.5</v>
+        <v>173.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>39.00515587591234</v>
+        <v>46.37578121156662</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>14.02737057194232</v>
+        <v>11.60702726947961</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.907688199020262</v>
+        <v>0.4989765271771578</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0482547932315254</v>
+        <v>1.5307086015519</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8096</v>
+        <v>8411</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>382.0193866373047</v>
+        <v>382.3215806818214</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>86.5</v>
+        <v>12.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>27.99575488903353</v>
+        <v>39.00515587591234</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>32.60940422968936</v>
+        <v>14.02737057194232</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7548333659731936</v>
+        <v>1.907688199020262</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.5038613205946341</v>
+        <v>-0.0482547932315254</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8487</v>
+        <v>8096</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>361.3188476410917</v>
+        <v>382.0193866373047</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>71.5</v>
+        <v>86.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>50.69751286141763</v>
+        <v>27.99575488903353</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>10.30866176713437</v>
+        <v>32.60940422968936</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.026946221095258</v>
+        <v>0.7548333659731936</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.1982762182020788</v>
+        <v>-0.5038613205946341</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8477</v>
+        <v>8358</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>350.603563512843</v>
+        <v>362.0860200005033</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>14.95</v>
+        <v>491.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>43.08375146442165</v>
+        <v>52.01592770314524</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>12.95851243651125</v>
+        <v>22.57553703365884</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2.207897884722831</v>
+        <v>0.1257712531639931</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.0412543372841466</v>
+        <v>-4.583993357754338</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>9912</v>
+        <v>8487</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>346.927804864736</v>
+        <v>361.3188476410917</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>12.95</v>
+        <v>71.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>50.73496141198085</v>
+        <v>50.69751286141763</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>29.32905583741327</v>
+        <v>10.30866176713437</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.217154751035471</v>
+        <v>1.026946221095258</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0007321790021781001</v>
+        <v>0.1982762182020788</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8443</v>
+        <v>8477</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>342.4411043815471</v>
+        <v>350.603563512843</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>11.25</v>
+        <v>14.95</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>47.52481777398297</v>
+        <v>43.08375146442165</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>50.57597780049352</v>
+        <v>12.95851243651125</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5523594387120241</v>
+        <v>2.207897884722831</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0058370599070259</v>
+        <v>-0.0412543372841466</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8068</v>
+        <v>9912</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>340.5515644965525</v>
+        <v>346.927804864736</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>16.05</v>
+        <v>12.95</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>34.33318135226575</v>
+        <v>50.73496141198085</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>23.03620428523274</v>
+        <v>29.32905583741327</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7690209499822227</v>
+        <v>0.217154751035471</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0182658954315069</v>
+        <v>0.0007321790021781001</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8271</v>
+        <v>8443</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>340.1299408457168</v>
+        <v>342.4411043815471</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>204</v>
+        <v>11.25</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>40.3411999829242</v>
+        <v>47.52481777398297</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>14.30971107024989</v>
+        <v>50.57597780049352</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4137762120977379</v>
+        <v>0.5523594387120241</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-1.876897541442053</v>
+        <v>0.0058370599070259</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8464</v>
+        <v>8068</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>339.9625377205084</v>
+        <v>340.5515644965525</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>370</v>
+        <v>16.05</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>48.55125486731235</v>
+        <v>34.33318135226575</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>14.8163053704564</v>
+        <v>23.03620428523274</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.533177611008646</v>
+        <v>0.7690209499822227</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.1405411939779148</v>
+        <v>-0.0182658954315069</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8163</v>
+        <v>8271</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>338.9168073219333</v>
+        <v>340.1299408457168</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>30.4</v>
+        <v>204</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46.47693273412867</v>
+        <v>40.3411999829242</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>16.78583972533533</v>
+        <v>14.30971107024989</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.7160764210619206</v>
+        <v>0.4137762120977379</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0526746367210441</v>
+        <v>-1.876897541442053</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8926</v>
+        <v>8464</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>336.597994923993</v>
+        <v>339.9625377205084</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>59.5</v>
+        <v>370</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>54.5511256464313</v>
+        <v>48.55125486731235</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>17.70792588770534</v>
+        <v>14.8163053704564</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.161046140368811</v>
+        <v>1.533177611008646</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.5023372892109614</v>
+        <v>-0.1405411939779148</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8423</v>
+        <v>8163</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>335.0172067802112</v>
+        <v>338.9168073219333</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>18</v>
+        <v>30.4</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>52.0306006357827</v>
+        <v>46.47693273412867</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>25.42844851645086</v>
+        <v>16.78583972533533</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.2352731087747494</v>
+        <v>0.7160764210619206</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0283187219688476</v>
+        <v>0.0526746367210441</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8049</v>
+        <v>8926</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>325.1971256153491</v>
+        <v>336.597994923993</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>24.45</v>
+        <v>59.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>40.16948288712495</v>
+        <v>54.5511256464313</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>20.026798285016</v>
+        <v>17.70792588770534</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.657340470292296</v>
+        <v>1.161046140368811</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0674588020548901</v>
+        <v>0.5023372892109614</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8121</v>
+        <v>8423</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>324.844171550873</v>
+        <v>335.0172067802112</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>27.7</v>
+        <v>18</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>47.0298354693645</v>
+        <v>52.0306006357827</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>19.81069913864904</v>
+        <v>25.42844851645086</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6873418370438032</v>
+        <v>0.2352731087747494</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.3162276940964934</v>
+        <v>-0.0283187219688476</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8440</v>
+        <v>8049</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>320.7458097312826</v>
+        <v>325.1971256153491</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>20</v>
+        <v>24.45</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>47.64851727860633</v>
+        <v>40.16948288712495</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>12.33304390215584</v>
+        <v>20.026798285016</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.466812848056564</v>
+        <v>1.657340470292296</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.009908595714278001</v>
+        <v>0.0674588020548901</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8249</v>
+        <v>8121</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>304.9167308066927</v>
+        <v>324.844171550873</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>39.35</v>
+        <v>27.7</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45.82951423330091</v>
+        <v>47.0298354693645</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>23.53266047310321</v>
+        <v>19.81069913864904</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5976224237983093</v>
+        <v>0.6873418370438032</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0835784985969303</v>
+        <v>0.3162276940964934</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8482</v>
+        <v>8440</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>304.7959288573292</v>
+        <v>320.7458097312826</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>48.4</v>
+        <v>20</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.18965235930745</v>
+        <v>47.64851727860633</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>3.683110142149245</v>
+        <v>12.33304390215584</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5795928857329151</v>
+        <v>1.466812848056564</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.1440623501987155</v>
+        <v>-0.009908595714278001</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8069</v>
+        <v>8249</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>297.9356792796278</v>
+        <v>304.9167308066927</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>144.5</v>
+        <v>39.35</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,49 +3785,49 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>34.19503979070282</v>
+        <v>45.82951423330091</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>31.93976958415455</v>
+        <v>23.53266047310321</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.9243739398258544</v>
+        <v>0.5976224237983093</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.7433926205635473</v>
+        <v>0.0835784985969303</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8114</v>
+        <v>8482</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>294.7707229865541</v>
+        <v>304.7959288573292</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>177.5</v>
+        <v>48.4</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>36.59163887307548</v>
+        <v>51.18965235930745</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>25.15276655750496</v>
+        <v>3.683110142149245</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.8548575140528385</v>
+        <v>0.5795928857329151</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.2171233195354158</v>
+        <v>-0.1440623501987155</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8374</v>
+        <v>8069</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>294.4788199922999</v>
+        <v>297.9356792796278</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>144.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,49 +3891,49 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>42.9869353937402</v>
+        <v>34.19503979070282</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>9.574393772652281</v>
+        <v>31.93976958415455</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.7033377404896385</v>
+        <v>0.9243739398258544</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.3308555184950715</v>
+        <v>0.7433926205635473</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8478</v>
+        <v>8114</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>284.6888672665153</v>
+        <v>294.7707229865541</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>140</v>
+        <v>177.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>40.85475919270015</v>
+        <v>36.59163887307548</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>7.667481148127784</v>
+        <v>25.15276655750496</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.046072190402607</v>
+        <v>0.8548575140528385</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.2417136520812572</v>
+        <v>-0.2171233195354158</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8404</v>
+        <v>8374</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>284.3653690054872</v>
+        <v>294.4788199922999</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>13.85</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>24.3187317787056</v>
+        <v>42.9869353937402</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>37.35663360996024</v>
+        <v>9.574393772652281</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3365369005487191</v>
+        <v>0.7033377404896385</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.1690813806096951</v>
+        <v>-0.3308555184950715</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8046</v>
+        <v>8478</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>281.1168926017956</v>
+        <v>284.6888672665153</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>1060</v>
+        <v>140</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45.06248809134127</v>
+        <v>40.85475919270015</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>13.80211919352176</v>
+        <v>7.667481148127784</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.208905739414436</v>
+        <v>1.046072190402607</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-5.182105968776487</v>
+        <v>0.2417136520812572</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8410</v>
+        <v>8404</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>279.0001848211263</v>
+        <v>284.3653690054872</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>29</v>
+        <v>13.85</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>35.25028855647663</v>
+        <v>24.3187317787056</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>36.59515739419124</v>
+        <v>37.35663360996024</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.583430725534328</v>
+        <v>0.3365369005487191</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0207295326330466</v>
+        <v>-0.1690813806096951</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8081</v>
+        <v>8046</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>278.5389242609229</v>
+        <v>281.1168926017956</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>250.5</v>
+        <v>1060</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46.2488415241076</v>
+        <v>45.06248809134127</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>19.14676441919419</v>
+        <v>13.80211919352176</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5565269044887899</v>
+        <v>1.208905739414436</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.3530115646015113</v>
+        <v>-5.182105968776487</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8085</v>
+        <v>8410</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>278.459188406227</v>
+        <v>279.0001848211263</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>14.45</v>
+        <v>29</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>55.48749603168724</v>
+        <v>35.25028855647663</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19.96051244836535</v>
+        <v>36.59515739419124</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.1942736328378031</v>
+        <v>2.583430725534328</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.1996295657225807</v>
+        <v>-0.0207295326330466</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8341</v>
+        <v>8081</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>276.7127121147072</v>
+        <v>278.5389242609229</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>74.8</v>
+        <v>250.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>44.86015848594513</v>
+        <v>46.2488415241076</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>11.23869082526632</v>
+        <v>19.14676441919419</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5375297250250077</v>
+        <v>0.5565269044887899</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0189413287067737</v>
+        <v>0.3530115646015113</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>9105</v>
+        <v>8085</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>274.817871595979</v>
+        <v>278.459188406227</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>8.380000000000001</v>
+        <v>14.45</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>46.17499628148156</v>
+        <v>55.48749603168724</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>16.68343760417354</v>
+        <v>19.96051244836535</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6626697277674708</v>
+        <v>0.1942736328378031</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0311893131196952</v>
+        <v>-0.1996295657225807</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8462</v>
+        <v>8341</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>272.2692070218288</v>
+        <v>276.7127121147072</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>161.5</v>
+        <v>74.8</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>43.13713460993344</v>
+        <v>44.86015848594513</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>23.80624026500449</v>
+        <v>11.23869082526632</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.2563179485172794</v>
+        <v>0.5375297250250077</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.7965472009161678</v>
+        <v>0.0189413287067737</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8105</v>
+        <v>9105</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>272.048916504307</v>
+        <v>274.817871595979</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>15.1</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>46.44038271258136</v>
+        <v>46.17499628148156</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>27.85771470136803</v>
+        <v>16.68343760417354</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.3146140525809891</v>
+        <v>0.6626697277674708</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.08009800205994951</v>
+        <v>-0.0311893131196952</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8071</v>
+        <v>8462</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>269.5503338871604</v>
+        <v>272.2692070218288</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>22.1</v>
+        <v>161.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>43.50585016842408</v>
+        <v>43.13713460993344</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15.89917966579326</v>
+        <v>23.80624026500449</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.4131740495498258</v>
+        <v>0.2563179485172794</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0590844207648284</v>
+        <v>-0.7965472009161678</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8093</v>
+        <v>8105</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>269.2074865996761</v>
+        <v>272.048916504307</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>24.5</v>
+        <v>15.1</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>50.89333743607736</v>
+        <v>46.44038271258136</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>16.16849518950721</v>
+        <v>27.85771470136803</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.596315673181711</v>
+        <v>0.3146140525809891</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0817807600136711</v>
+        <v>0.08009800205994951</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8473</v>
+        <v>8071</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>268.8536076425834</v>
+        <v>269.5503338871604</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>38.7</v>
+        <v>22.1</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>33.77585171848457</v>
+        <v>43.50585016842408</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>32.44121538373209</v>
+        <v>15.89917966579326</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5497925684099417</v>
+        <v>0.4131740495498258</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.450797823394766</v>
+        <v>-0.0590844207648284</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8112</v>
+        <v>8093</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>265.18711531004</v>
+        <v>269.2074865996761</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>83.09999999999999</v>
+        <v>24.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>35.30873283204262</v>
+        <v>50.89333743607736</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>19.83394186012826</v>
+        <v>16.16849518950721</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5230210310314287</v>
+        <v>0.596315673181711</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.7209080267113868</v>
+        <v>-0.0817807600136711</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8101</v>
+        <v>8473</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>262.6475448752155</v>
+        <v>268.8536076425834</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>11.25</v>
+        <v>38.7</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>46.45447417888869</v>
+        <v>33.77585171848457</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>6.065805769184274</v>
+        <v>32.44121538373209</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.252052538112437</v>
+        <v>0.5497925684099417</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0661960453560774</v>
+        <v>-0.450797823394766</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8155</v>
+        <v>8112</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>250.8900397385578</v>
+        <v>265.18711531004</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>327.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>48.189888896631</v>
+        <v>35.30873283204262</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>16.58635573182449</v>
+        <v>19.83394186012826</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.5041029210497281</v>
+        <v>0.5230210310314287</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-3.420072075667242</v>
+        <v>-0.7209080267113868</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4767,21 +4767,21 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8074</v>
+        <v>8101</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>245.4605743296752</v>
+        <v>262.6475448752155</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>50.9</v>
+        <v>11.25</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>42.28028189307356</v>
+        <v>46.45447417888869</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>19.7979288739119</v>
+        <v>6.065805769184274</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.7138059024560062</v>
+        <v>0.252052538112437</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.1409391280685059</v>
+        <v>-0.0661960453560774</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8176</v>
+        <v>8155</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>245.1920487634013</v>
+        <v>250.8900397385578</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>327.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>49.64872926608397</v>
+        <v>48.189888896631</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>19.11121088646453</v>
+        <v>16.58635573182449</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.9018408263465744</v>
+        <v>0.5041029210497281</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.007934554220394</v>
+        <v>-3.420072075667242</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8454</v>
+        <v>8074</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>244.4462421621125</v>
+        <v>245.4605743296752</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>246.5</v>
+        <v>50.9</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>48.11902024003953</v>
+        <v>42.28028189307356</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>10.42306832138018</v>
+        <v>19.7979288739119</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.9805338338709978</v>
+        <v>0.7138059024560062</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>1.406198792825058</v>
+        <v>-0.1409391280685059</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>9802</v>
+        <v>8176</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>238.8481317785904</v>
+        <v>245.1920487634013</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>63.6</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>28.42049546330847</v>
+        <v>49.64872926608397</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>21.89580965443552</v>
+        <v>19.11121088646453</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.023757439725217</v>
+        <v>0.9018408263465744</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.5684536731534457</v>
+        <v>0.007934554220394</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>9930</v>
+        <v>8454</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>236.2639230955761</v>
+        <v>244.4462421621125</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>60.7</v>
+        <v>246.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>29.99653115097754</v>
+        <v>48.11902024003953</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>24.64176150122282</v>
+        <v>10.42306832138018</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.407862511749534</v>
+        <v>0.9805338338709978</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1619075685671488</v>
+        <v>1.406198792825058</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8076</v>
+        <v>9802</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>213.7636995645337</v>
+        <v>238.8481317785904</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>21.6</v>
+        <v>63.6</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>38.24392222867886</v>
+        <v>28.42049546330847</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>23.91347845372045</v>
+        <v>21.89580965443552</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5494275613490213</v>
+        <v>1.023757439725217</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0238907454224822</v>
+        <v>-0.5684536731534457</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8087</v>
+        <v>9930</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>208.577392851679</v>
+        <v>236.2639230955761</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>24.3</v>
+        <v>60.7</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>50.73133152244627</v>
+        <v>29.99653115097754</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>8.492925592731844</v>
+        <v>24.64176150122282</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.8232150887495702</v>
+        <v>1.407862511749534</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.519953310402458</v>
+        <v>-0.1619075685671488</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8367</v>
+        <v>8076</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>206.3216208508253</v>
+        <v>213.7636995645337</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>40.65</v>
+        <v>21.6</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>49.77298250894938</v>
+        <v>38.24392222867886</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>21.46786620999765</v>
+        <v>23.91347845372045</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.281661922119786</v>
+        <v>0.5494275613490213</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0164484094098988</v>
+        <v>-0.0238907454224822</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8084</v>
+        <v>8087</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>204.0616827220869</v>
+        <v>208.577392851679</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>40.6</v>
+        <v>24.3</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>30.64998769143535</v>
+        <v>50.73133152244627</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>19.19447381827653</v>
+        <v>8.492925592731844</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.233530877394638</v>
+        <v>0.8232150887495702</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.4892462580908272</v>
+        <v>0.519953310402458</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8088</v>
+        <v>8367</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>200.6463079466761</v>
+        <v>206.3216208508253</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>43.35</v>
+        <v>40.65</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45.1140369494135</v>
+        <v>49.77298250894938</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>13.25574335897089</v>
+        <v>21.46786620999765</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.7506710953471871</v>
+        <v>1.281661922119786</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.1695948797711093</v>
+        <v>-0.0164484094098988</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8481</v>
+        <v>8084</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>197.8682037850021</v>
+        <v>204.0616827220869</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>41</v>
+        <v>40.6</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>50.31473585041869</v>
+        <v>30.64998769143535</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12.33119318929085</v>
+        <v>19.19447381827653</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.907013134020275</v>
+        <v>1.233530877394638</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0130379687204392</v>
+        <v>-0.4892462580908272</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8422</v>
+        <v>8088</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>197.0083895861096</v>
+        <v>200.6463079466761</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>26</v>
+        <v>43.35</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45.01950119064292</v>
+        <v>45.1140369494135</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>10.51190483153781</v>
+        <v>13.25574335897089</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.007226503839551</v>
+        <v>0.7506710953471871</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.02863384864683</v>
+        <v>0.1695948797711093</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8455</v>
+        <v>8481</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>196.3361900950277</v>
+        <v>197.8682037850021</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>22.7</v>
+        <v>41</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>50.96552694034151</v>
+        <v>50.31473585041869</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>10.5153255642082</v>
+        <v>12.33119318929085</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6457792941632314</v>
+        <v>1.907013134020275</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.1770233266076284</v>
+        <v>-0.0130379687204392</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8067</v>
+        <v>8422</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>195.430081650433</v>
+        <v>197.0083895861096</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>11.85</v>
+        <v>26</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>43.45375010883713</v>
+        <v>45.01950119064292</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>16.73150607953102</v>
+        <v>10.51190483153781</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4650164805565954</v>
+        <v>1.007226503839551</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0176262536861789</v>
+        <v>-0.02863384864683</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>9110</v>
+        <v>8455</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>192.732394425932</v>
+        <v>196.3361900950277</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>2.9</v>
+        <v>22.7</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>51.93095137698416</v>
+        <v>50.96552694034151</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>6.271579189024518</v>
+        <v>10.5153255642082</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>7.061786162451879</v>
+        <v>0.6457792941632314</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.07209814291798371</v>
+        <v>-0.1770233266076284</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8210</v>
+        <v>8067</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>192.6109654427589</v>
+        <v>195.4300816504329</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>900</v>
+        <v>11.85</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>39.93226923682165</v>
+        <v>43.45375010883713</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>19.39172228931449</v>
+        <v>16.73150607953102</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.7557266784269924</v>
+        <v>0.4650164805565954</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>2.749346512711768</v>
+        <v>-0.0176262536861789</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8092</v>
+        <v>9110</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>184.6066492748974</v>
+        <v>192.732394425932</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>12.7</v>
+        <v>2.9</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>42.69180420591681</v>
+        <v>51.93095137698416</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>11.58804446405565</v>
+        <v>6.271579189024518</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.7408916146115074</v>
+        <v>7.061786162451879</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0002510495941497</v>
+        <v>0.07209814291798371</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8499</v>
+        <v>8210</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>182.7869216683899</v>
+        <v>192.6109654427589</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>255</v>
+        <v>900</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>51.25832104731964</v>
+        <v>39.93226923682165</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>11.83475364227566</v>
+        <v>19.39172228931449</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.4641022893217766</v>
+        <v>0.7557266784269924</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.9410809432778268</v>
+        <v>2.749346512711768</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>9103</v>
+        <v>8092</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>182.0798914658036</v>
+        <v>184.6066492748974</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>4.98</v>
+        <v>12.7</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>40.93223778229835</v>
+        <v>42.69180420591681</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>12.38563582333373</v>
+        <v>11.58804446405565</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.056879759622307</v>
+        <v>0.7408916146115074</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0057911271250566</v>
+        <v>-0.0002510495941497</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>9136</v>
+        <v>8499</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>159.4141232282173</v>
+        <v>182.7869216683899</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>9.720000000000001</v>
+        <v>255</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>34.19930023412417</v>
+        <v>51.25832104731964</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.10416318500859</v>
+        <v>11.83475364227566</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.179684844121823</v>
+        <v>0.4641022893217766</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0615167358525899</v>
+        <v>-0.9410809432778268</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8234</v>
+        <v>9103</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>151.6302154446278</v>
+        <v>182.0798914658036</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>62.5</v>
+        <v>4.98</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>40.28258304327238</v>
+        <v>40.93223778229835</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18.46978250929997</v>
+        <v>12.38563582333373</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.4137472636139965</v>
+        <v>1.056879759622307</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.4437441927244465</v>
+        <v>-0.0057911271250566</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8438</v>
+        <v>9136</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>150.9134601370449</v>
+        <v>159.4141232282173</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>69</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>50.08019374571597</v>
+        <v>34.19930023412417</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>14.02952832954157</v>
+        <v>17.10416318500859</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.7083590901383591</v>
+        <v>1.179684844121823</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.1294123512955696</v>
+        <v>-0.0615167358525899</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8044</v>
+        <v>8234</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>140.2041946858353</v>
+        <v>151.6302154446278</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>24.05</v>
+        <v>62.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>46.06050088160752</v>
+        <v>40.28258304327238</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>16.30048547510127</v>
+        <v>18.46978250929997</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.486170642362857</v>
+        <v>0.4137472636139965</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.125608506168967</v>
+        <v>-0.4437441927244465</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8476</v>
+        <v>8438</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>134.7494521842289</v>
+        <v>150.9134601370449</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>19.5</v>
+        <v>69</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>44.77982143493932</v>
+        <v>50.08019374571597</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>9.838050311194612</v>
+        <v>14.02952832954157</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.8877851707585488</v>
+        <v>0.7083590901383591</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.07256403921914931</v>
+        <v>0.1294123512955696</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8429</v>
+        <v>8044</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>133.8983651270898</v>
+        <v>140.2041946858353</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>5.91</v>
+        <v>24.05</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>38.52560884041745</v>
+        <v>46.06050088160752</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>6.156942523856664</v>
+        <v>16.30048547510127</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5678303137428192</v>
+        <v>1.486170642362857</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0026785434597402</v>
+        <v>0.125608506168967</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6092,21 +6092,21 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>9955</v>
+        <v>8476</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>131.6380871210282</v>
+        <v>134.7494521842289</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>23.4</v>
+        <v>19.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>41.44145104242291</v>
+        <v>44.77982143493932</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>10.42896721518297</v>
+        <v>9.838050311194612</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.694021010523186</v>
+        <v>0.8877851707585488</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0194286230281285</v>
+        <v>0.07256403921914931</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8390</v>
+        <v>8429</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>129.1588129551466</v>
+        <v>133.8983651270898</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>91.8</v>
+        <v>5.91</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>37.75773709217032</v>
+        <v>38.52560884041745</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>16.03804396742206</v>
+        <v>6.156942523856664</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3740253933665038</v>
+        <v>0.5678303137428192</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.4250636117486972</v>
+        <v>-0.0026785434597402</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8291</v>
+        <v>9955</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>127.8411208439491</v>
+        <v>131.6380871210282</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>29.45</v>
+        <v>23.4</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>42.03532620512523</v>
+        <v>41.44145104242291</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>8.541095621420247</v>
+        <v>10.42896721518297</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.9139474444123592</v>
+        <v>0.694021010523186</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.1186443584910215</v>
+        <v>-0.0194286230281285</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8102</v>
+        <v>8390</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>126.2723069272976</v>
+        <v>129.1588129551466</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>61</v>
+        <v>91.8</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>50.15810473871625</v>
+        <v>37.75773709217032</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>6.511852432696939</v>
+        <v>16.03804396742206</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.3819223424570337</v>
+        <v>0.3740253933665038</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.4939798315936814</v>
+        <v>-0.4250636117486972</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8940</v>
+        <v>8291</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>99.57263457828482</v>
+        <v>127.8411208439491</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>15</v>
+        <v>29.45</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>46.71113575989396</v>
+        <v>42.03532620512523</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>8.93116677777712</v>
+        <v>8.541095621420247</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.445460293687832</v>
+        <v>0.9139474444123592</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0328027262257928</v>
+        <v>0.1186443584910215</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8463</v>
+        <v>8102</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>99.41122176604009</v>
+        <v>126.2723069272976</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>21.25</v>
+        <v>61</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>48.98327025844788</v>
+        <v>50.15810473871625</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>18.97070817512222</v>
+        <v>6.511852432696939</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.8800415910066982</v>
+        <v>0.3819223424570337</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0267852715319313</v>
+        <v>0.4939798315936814</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8467</v>
+        <v>8940</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>67.72848379396346</v>
+        <v>99.57263457828482</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>15</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>48.14394551959116</v>
+        <v>46.71113575989396</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11.1766828725887</v>
+        <v>8.93116677777712</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.3897867550803185</v>
+        <v>0.445460293687832</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.647087497527508</v>
+        <v>0.0328027262257928</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>9902</v>
+        <v>8463</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>64.96668351550977</v>
+        <v>99.41122176604009</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>13.4</v>
+        <v>21.25</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>43.90655188089367</v>
+        <v>48.98327025844788</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14.66118976615117</v>
+        <v>18.97070817512222</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.7254457941991619</v>
+        <v>0.8800415910066982</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0221961176750761</v>
+        <v>-0.0267852715319313</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,52 +6516,158 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
+        <v>8467</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>波力-KY</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>67.72848379396346</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>48.14394551959116</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>11.1766828725887</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.3897867550803185</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>0.647087497527508</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>9902</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>台火</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>64.96668351550977</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>43.90655188089367</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>14.66118976615117</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.7254457941991619</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.0221961176750761</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
         <v>8222</v>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>寶一</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D115" s="2" t="n">
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
         <v>62.62596696298573</v>
       </c>
-      <c r="E115" s="2" t="n">
+      <c r="E117" s="2" t="n">
         <v>35.75</v>
       </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H115" s="2" t="n">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
         <v>43.30312380018424</v>
       </c>
-      <c r="I115" s="2" t="n">
+      <c r="I117" s="2" t="n">
         <v>14.95805064589396</v>
       </c>
-      <c r="J115" s="2" t="n">
+      <c r="J117" s="2" t="n">
         <v>0.4268678881157645</v>
       </c>
-      <c r="K115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N115" s="2" t="n">
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
         <v>-0.0968014391564733</v>
       </c>
-      <c r="O115" s="2" t="inlineStr">
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
